--- a/RESULTS/datawos_scopus_repeatedstitles.xlsx
+++ b/RESULTS/datawos_scopus_repeatedstitles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A93"/>
+  <dimension ref="A1:A322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,644 +438,2247 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>accurate prediction crop yield hybrid deep capsule auto encoder softmax regression</t>
+          <t>accessibility trust dimension consumer perception sustainable purchase intention</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>adaptive neuro fuzzy inference system base multicrop yield prediction semi arid region india</t>
+          <t>achieve sustainable procurement construction project pivotal role project management office</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>aienhanced remote sensing application indian sugarcane research comprehensive review</t>
+          <t>address organisational pressure driver sustainability manufacturing project project management methodology</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>annual fieldscale map tall short crop global scale gedi sentinel</t>
+          <t>advance digital project management ai interpretable poalightgbm framework cost overrun prediction</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>application machine learning technology feedstock yield estimation ethanol production</t>
+          <t>ambidextrous leadership drive sustainable project performance green knowledge innovation</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>artificial intelligence sugarcane breed comprehensive review application tool future prospect</t>
+          <t>ambidextrous leadership drive sustainable project performance product innovativeness environmental feature boundary condition</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>artificial neural network model predict behavior biogas production curve mix lignocellulosic cosubstrate</t>
+          <t>analytical framework investigate ethic social responsibility sustainability engineering project management</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>assess impact climate variability australias sugarcane yield</t>
+          <t>analyze driver conflict energy infrastructure project empirical case study natural gas pipeline sector</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>automate estimation crop yield artificial intelligence remote sensing technology</t>
+          <t>analyze driver sustainable projectdriven supply chain fuzzy delphi methodologygrey relational analysis approach</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>canopy segmentation accurate prediction uavbase multifeature fusion framework plotscale ratoon sugarcane seedling counting</t>
+          <t>antecedent consequence sustainable project management evidence construction industry china</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>classification horticultural crop high resolution multispectral imagery deep learning approach</t>
+          <t>application fuzzy analytic hierarchy process sustainable project selection</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>classification sugarcane variety harmonize sentinel landsat datum parametric nonparametric method</t>
+          <t>apply prism methodology raise awareness importance sustainable project management practice organization</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>climate altitude yield variety drive lodging sugarcane random forest approach predict risk level tropical island</t>
+          <t>appraise triple line utility sustainable project portfolio selection novel multicriteria house portfolio</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>climate variability impact crop yield agriculture contribution gross domestic product nile basin deep machine learning algorithm tell</t>
+          <t>approach project framework environment sustainability corporate social responsibility csr case study training proposal group student high education institution</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cnn ensemble approach early detection sugarcane disease comparison</t>
+          <t>assess stability relationship party crowdfunde crowdsourcing project covid crisis</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>comparative assessment artificial neural network response surface modelling efficiency biohydrogen production sugar cane molasses</t>
+          <t>assessment effect size social indicator sustainability context international rural development project iran baci framework</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>consequence data uncertainty data precision artificial neural network sugar cane yield prediction</t>
+          <t>assessment preconstruction factor sustainable project management performance</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>crop yield prediction base machine learning</t>
+          <t>assessment regional development need accord criterion base sustainable development goal meta region colombia</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>crop yield prediction india base mayfly optimization empower attentionbidirectional long shortterm memory lstm</t>
+          <t>assessment sustainability performance ecoengineere measure mediterranean region</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>datadriven earlyseason forecast block sugarcane yield precision agriculture</t>
+          <t>assessment sustainability real estate project multicriteria decision make</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>datadriven machine learning framework predict total agricultural food grain yield</t>
+          <t>assessment triple line sustainability geotechnical project</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>design sugarcane yield productivity prediction model</t>
+          <t>assessment visual value tool support design decision cultural park protection plan case kazimierz stradom krakow</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>digital soil mapping output soil classification sugarcane production brazil</t>
+          <t>barrier impede sustainable project management social network analysis iranian construction sector</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>dscapspnet dynamic spatialchannel attention pyramid scene parse network sugarcane field segmentation satellite imagery</t>
+          <t>barrier implement environmental sustainability uae construction project management identification comparison iso certify noncertified firm</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>effect tune feature engineering feature selection datum mining apply rainfed sugarcane yield modelling</t>
+          <t>barrier sustainable construction project management case iran</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>empirical model forecasting sugarcane yield local scale brazil landsat imagery random forest algorithm</t>
+          <t>behavioral barrier sustainable action project management overcome</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>energising economy global impact indian sugar</t>
+          <t>benefit adopt innovation sustainability practice project management sme context</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>estimate sugarcane productivity machine learning algorithm time series wficber wpmcbersa time series</t>
+          <t>bim integration high education global assessment</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>estimation sugarcane yield machine learning approach base uavlidar datum</t>
+          <t>biobjective scheduling optimization discrete timecost tradeoff project</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>estimation sugarcane yield multitemporal sentinel satellite imagery random forest regression</t>
+          <t>biocenosis novel framework sustainability assessment build environment indian context</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>evaluate statistical machine learning technique sugarcane yield forecasting tarai region north india</t>
+          <t>borehole investigation steep slope ground</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>evaluate sugarcane yield estimation thailand multitemporal sentinel landsat datum machinelearne algorithm</t>
+          <t>building criterion evaluate green project management integrate approach dematel anp</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>fieldscale estimation comparison sugarcane yield remote sensing datum machine learning approach</t>
+          <t>carbon footprint railway project belt road initiative future lowcarbon pathway</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>forecast sugarcane yield chongzuo guangxilstm model base fusion trend yield meteorological yield</t>
+          <t>carmine maggiore bell tower inclusive sustainable restoration experience</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>forecasting sugarcane yield base meteorological datum ensemble learn</t>
+          <t>certification tool develop sustainability project management</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>fuzzy modeling particle swarm optimization determine optimal operating parameter enhance biomethanol production sugar cane bagasse</t>
+          <t>challenge introduce sustainability project management function multiplecase study</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>high accuracy preharv sugarcane yield forecasting model utilize drone image analysis datum mining reverse design method</t>
+          <t>characteristic perception project management productive sector sustainable future</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>highprecision sugarcane yield prediction integrate m sentinel vod sentinel grvi index</t>
+          <t>circularity cost framework offsite housing project</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>hybrid cnnsvm classifier approach process semistructure data sugarcane yield forecasting production</t>
+          <t>citywide health promotion programme evaluation equihp jerusalem communityacademic partnership jcap</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>hybrid learn fuzzy cognitive map sugarcane yield classification</t>
+          <t>classify level bid price volatility base machine learning parameter bid document risk factor</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>implementation longterm forecasting model sugarcane agricultural planning yield goal set</t>
+          <t>collective efficacybase approach biobjective sustainable project portfolio selection interdependency network model project</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>implementation rsm ann optimization approach valorization agrowaste renewable plastic precursor fdca nonprecious bimetal oxide functionalize heterogeneous catalyst</t>
+          <t>communitys desire critical look participatory research project indigenous community</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>integrate advance nonlinear neural networksimulink control system production biomethanol sugar cane bagasse pyrolysis</t>
+          <t>comparison housing construction system huasteca zone vernacular industrialize hybrid study case</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>integrate landsat sentinel time series datum yield prediction sugarcane crop block level</t>
+          <t>competency capabilitie management sustainable rural development project value chain perception small mediumsized business agent jauja peru</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>integrate satellite imagery environmental datum predict fieldlevel cane sugar yield australia machine learning</t>
+          <t>complex approach environmental technological project management enhance sustainability industrial system</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>integration remote sense meteorological datum rapid sugarcane yield estimation machine learn</t>
+          <t>comprehensive mathematical model resourceconstraine multiobjective project portfolio selection scheduling consider sustainability project split</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>investigate capability dove satellite temporal datum mapping harvest date sugarcane crop type fuzzy model</t>
+          <t>computerbase scaffolding sustainable projectbased learning impact high lowachieve student</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>investigate early identifiable timing sugarcane early season base optical sar timeseries datum</t>
+          <t>conceptual framework sustainable construction arab region</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>leverage blend machine learning model sugarcane crop yield estimation predictive insight precision agriculture</t>
+          <t>conceptualize sustainability governance implementation infrastructure delivery system develop country success factor</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>machine learning method crop yield prediction</t>
+          <t>consider sustainability project management decision make investigation qmethodology</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>machine learning model ensemble predict sugarcane yield synergy optical sar remote sensing</t>
+          <t>consideration sustainability project crosssectional quantitative analysis</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>machine learningbase crop yield prediction south india performance analysis model</t>
+          <t>construct validation approach explore sustainability adoption pakistani construction project</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>machinelearningbase regional yield forecasting sugarcane crop uttar pradesh india</t>
+          <t>construction practice knowledge complement classroom teaching site visit</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>metafeature extract use knn regressor improve sugarcane crop yield prediction</t>
+          <t>contribution project management sustainable society explore perception project manager</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>model sugarcane bagasse conversion levulinic acid response surface methodology rsm artificial neural network ann fuzzy inference system fis comparative evaluation</t>
+          <t>corporate sustainability investment capital structure</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>modeling optimization activate carbon yield sugarcane bagasse rsm machine learning</t>
+          <t>corporate sustainability stakeholder value tradeoff project selection optimization modeling application investment banking</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>open set semantic segmentation multitemporal crop recognition</t>
+          <t>critical success factor csfs integration sustainability construction project management practice develop country</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>operational framework predict field level crop biomass remote sensing datum drive model</t>
+          <t>critical success factor sustainable project management construction fuzzy dematelanp approach</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>optimization process variable torrefaction coalbiomasswaste tyre blend application artificial neural network response surface methodology</t>
+          <t>crowdfunding business model lens sustainable development taxonomy backer funder</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>overview sugarcane agroindustry colombia sustainable journey current challenge</t>
+          <t>cumulative sustainability performance index contractor consultant prequalification system</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>performance evaluation sentinel imagery agronomic climatic datum sugarcane yield estimation</t>
+          <t>cybernetic model design qualification pharmaceutical facility</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>plot level sugarcane yield estimation machine learn multispectral image case study bundaberg australia</t>
+          <t>datadriven decision make sustainable project management excellence</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>population dynamic estimation damage spittlebug aeneolamia varia sugarcane colombia remote sensing machine learning tool</t>
+          <t>datadriven public rd project performance evaluation result china</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>potential use machine learn sugarcane production thailand review</t>
+          <t>decision approach analyse role modern method project management integrate approach environmentally sustainable construction project</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>predict sugarcane biometric parameter uav multispectral image machine learn</t>
+          <t>decisionmaking algorithm proposal assess project management adherence sustainable development goal pair comparison grey systemsbase approach</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>predict sugarcane yield temporal analysis satellite imagery growth phase</t>
+          <t>define successful project sustainable project management simulationa case study</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>predict sugarcane yield use improve square support vector machine water cycle optimization model</t>
+          <t>design bid build integrated project delivery strategic formulation increase partner</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>prediction method sugarcane important phenotype datum base multimodel multitask</t>
+          <t>determinant sustainable road infrastructure project implementation outcome develop country</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>prediction sugarcane disease data mining technique</t>
+          <t>determination project procurement method graphical analytic model</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>product quality monitoring extreme learn machine bat algorithm case study secondgeneration ethanol production</t>
+          <t>develop integrate conceptual framework sustainable public housing</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>prospect artificial intelligence sustainability sugarcane production modern era climate change overview relate global finding</t>
+          <t>develop maturity rating system project management office</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>recognition bloomyield crop image deep learning model smart agriculture review</t>
+          <t>develop model assess efficiency sustainable human resource management construction project</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>regional model predict sugarcane yield sentinel imagery paulo state brazil</t>
+          <t>develop projectexpectancy inventory construction industry owner perspective</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>remote sensing application sugarcane cultivation review</t>
+          <t>development delay disruption cause monitoring framework megaproject claim management approach contractor perspective enhance sustainability build environment</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>research fusion time series sentinel datum phenological feature sugarcane planting distribution extraction</t>
+          <t>development guideline implementation sustainable enterprise resource planning system</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>retract comparative study sugarcane average unit yield prediction genetic bp neural network algorithm retract article</t>
+          <t>difference publicsector privatesector project management practice hungary competency point view</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>satellitebased methodology harvest date detection yield prediction sugarcane</t>
+          <t>different method public management use cultural heritage los colorados provincial multiple use reserve la rioja argentina case study</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>sensitive multispectral variable screening method yield prediction model sugarcane base gray relational analysis correlation analysis</t>
+          <t>digital transformation naval industry</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>simplexcentroid design artificial neural networkgenetic algorithm optimization exoglucanase production penicillium roqueforti atcc solidstate fermentation blend agroindustrial waste</t>
+          <t>driver farmer behavior compensation scheme cultivate land protection chengdu pilot area china</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>sugarcane area mapping zero label hybrid unsupervised supervised approach</t>
+          <t>dwaspas address social cognition uncertain decisionmaking application sustainable project portfolio problem</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>sugarcane growth prediction base meteorological parameter extreme learn machine artificial neural network</t>
+          <t>dynamic portfolio selection gas transmission project consider sustainable strategic alignment project interdependency value analysis</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>sugarcane saccharum officinarum productivity estimation multispectral sensor rpas biometric variable vegetation index</t>
+          <t>effect blue agave agave tequilana weber management soil erosion</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>sugarcane varietal classification remote sensing ai comprehensive review future roadmap</t>
+          <t>effect implement sustainable management practice construction claim mitigation</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>sugarcane yield estimation remote sensing time series phenology metric</t>
+          <t>empower sustainable project management analyse barrier develop nation</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>sugarcane yield estimation thailand multiple scale integration uav sentinel imagery</t>
+          <t>empower urban sustainability unveil crucial role project manager attain sustainable development goal</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>sugarcane yield forecast ivory coast west africa base weather vegetation index datum</t>
+          <t>engineering design approach implement interdisciplinary integration sustainability energy material science experience rural multigrade elementary school</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>sugarcane yield mapping highresolution imagery datum machine learning technique</t>
+          <t>engineering machinelearning automation platform emap bigdatadriven ai tool contractor sustainable management solution plant project</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>sugarcane yield prediction brazil ndvi time series neural network ensemble</t>
+          <t>enhance decision make decarbonation environmental management review role digital technology</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>sustainable extraction mlbased yield prediction silica nanoparticle sugarcane bagasse groundnut shell functional surface coating</t>
+          <t>enhance performance agribusiness sustainable project management technological orientation institutional theory perspective</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>uav imagery datum machine learning drive merger predictive analysis qualitative yield sugarcane</t>
+          <t>enhance sustainability project management role stakeholder engagement knowledge management virtual team environment</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>yield commercial cane sugar estimation sugarcane thailand case study</t>
+          <t>etechnology enable source alternative fuel create fairtrade circular economy sustainable energy togo</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>yield forecasting sugarcane machine learn uavderive canopy height</t>
+          <t>evaluate decision make sustainable project selection literature practice</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>evaluate organizational sustainability multicriteria basedapproach sustainable project management indicator</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>evaluate sustainabilityrelated deliverable construction project lifecycle delphi study</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>evaluation barrier enabler integrative multicriteria decision mapping develop sustainable community energy indian context</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>evaluation factor affect competitive advantage organization establish sustainable project management post covid</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>evolve history sustainable project explore existential meaning agency level</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>examine impact risk management practice sustainable project performance construction industry role stakeholder engagement</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>executive sponsorship matter realize project management value</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>exploratory analysis project management corporate sustainability capability organizational success</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>explore characteristic sustainability stimulus pattern project manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>explore different pattern perceive barrier sustainable project management</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>explore gender difference sustainable project management competency awareness sustainable development goal sdgs</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>explore impact dynamic capability sustainable delivery international engineering project configurational approach</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>explore pattern sustainability stimulus project manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>explore project manager intention address sustainability project board</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>explore project owner behaviour address sustainability project assignment governance</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>explore relationship sustainable project institutional isomorphisms project typology</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>explore risk factor infrastructure ppp project sustainable delivery social network perspective</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>explore team member perception internal sustainability communication sustainable project management</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>explore validate effect mega project infrastructure development influence sustainable environment project management</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>explore value management implementation activity sustainable building project</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>explore value sustainable project manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>explore variety factor stimulate project manager address sustainability issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>family medicine diploma program jordan components success sustainability</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>feasibility sustainability separation drinking water network groundwater desalination bajestan urban catchment iran</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>feature architecturalrestoration activity take account aspect symbolism</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>financial impact replace plastic packaging biodegradable biopolymer smart solution food industry</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>foster green building project performance blockchainenable smart contract bsc implementation adaptive structuration perspective</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>framework account uncertainty energy carbon assessment ground improvement work</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>framework salvage megaproject africa base case study refinery petrochemical complex project</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>future construction integrate innovative technology smart project management</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>fuzzy decision support system sustainable construction project selection integrate fppfis model</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>fuzzy multiagent model project portfolio scheduling selection take account environmental resilience</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>gamebase learn project sustainability management education</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>global spatial suitability mapping wind solar system explainable aibased approach</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>go environmental regulationsthe influence firm size effect green practice corporate financial performance</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>govern publicprivate partnership sustainable construction project opportunistic setting</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>governance challenge marine renewable energy development create enable condition successful project development</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>green project management competency sustainable development goal sdgs empirical evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>green project management employee perspective hong kongs engineering construction sector</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>green project management practice green knowledge acquisition sustainable competitive advantage empirical evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>green smart city navigate net zero carbon construction sustainable practice innovation climate management support</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>green value engineering methodology sustainabilitydriven project management tool capital project process industry</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>group decisionmaking base aggregation approach intervalvalue pythagorean fuzzy environment sustainable project decision</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>harmonize project management supply chain sustainable construction comprehensive mathematical model case study</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>harness emotional cultural intelligence corporate sustainability indonesia examine psychological contract task interdependence environmentally sustainable project performance</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>history future project transition innovation sustainable project management framework</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>household willingness pay quality drinking water jaffna area sri lanka</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>hybrid project management traditional software development lifecycle agile base product development future sustainability</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>identification classification facility manager function proposal validate latin american expert</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>impact critical success factor supportive leadership sustainable success renewable energy project empirical evidence pakistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>impact project complexity trust leader performance readiness situational leadership financial sustainability</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>impact sustainability palliative care education module patient heart failure</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>impact sustainable project management project plan project success manufacture firm structural model assessment</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>imperative research direction sustainable project management</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>implement concurrent engineering qfd method achieve realization sustainable project</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>improve effectiveness organisational collaborative innovation megaproject agentbase modelling approach</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>improve sustainable project success strategy focus cost schedule electrical construction project management</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>incentive mechanism prefabrication mega project reputational concern</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>incorporate sustainability defense project evidence norway</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>incorporate sustainability software project conceptual framework</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>incorporation sustainability issue sustainable development goal project management catalyst sustainable project delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>influence technical reason cost overrun infrastructural project sustainable development perspective</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>information system project sustainability capabality level</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>innovation ecosystem paradox strong external support weaken project managementsustainability innovation link</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>innovative topdown construction method sequential peripheral wall</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>integrate bim machine learning pmbok green project management saudi arabia framework energy efficiency environmental impact reduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>integrate efficiencyrisk approach sustainable project control</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>integrate sustainability construction engineering project perspective sustainable project planning</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>integrate sustainability issue project management</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>integrate sustainability major infrastructure project perspective sustainable tunnel development</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>integration application importance collaboration sustainable project management</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>interactive visualization tool collaborative construction logistic planningcreate sustainable project vicinity</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>inventoryschedule problem sustainable project supply chain uncertainty</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>investigate nexus critical success factor despotic leadership success renewable energy project</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>investigate significance sustainability indicator promote sustainable construction project management</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>investigation heritage sustainability place attachment otatara case study</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>investigation perspective design education industry practice sustainability design</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>job performance burnout sustainable planning education project</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>key competency identify construction activity produce recyclable material competency gap analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>key factor sustainability project management context survey explore project manager perspective</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>key practice incorporate sustainability project management perspective brazilian professional</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>leadership core competency palliative carerecommendation european association palliative care delphi study</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>lean management framework achieve sustainability reduce risk design process</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>lean meet green uncover integration enabler lean construction management sustainable construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>lean sustainable project delivery building construction development conceptual framework</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>lesson design development implementation threedimensional d neonatal resuscitation train smartphone application lifesaving instruction emergency life app</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>leverage nfts sustainable urban finance challenge opportunitie smart city</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>link government support quality management sustainable energy project success mediate role community participation moderate role project governance</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>link sustainable leadership sustainable project performance mediate role knowledge integration moderate role management knowledge value</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>link sustainable project management construction project success moderate influence stakeholder engagement</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>linkage agile project management sustainable development theoretical empirical view</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>linkage renewable energy project management know future direction research</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>lose translation inadequate nontechnical risk assessment major project team mine</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>love climate sinopakistan economic romance perspective environmental law</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>manage material vendor risk improve project operational performance role riskoriente culture</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>manage project success project risk green supply chain management survey automotive industry</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>manage project sustainability extractive industry reciprocity framework community engagement</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>mapping knowledge domain stakeholder perspective study construction project bibliometric approach</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>mapping landscape esg integration projectoriente workplace crosssectional analysis professional organizational readiness</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>material order supplier selection sustainable project scheduling multicriteria decision make mathematical modelling approach</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>mathematical model optimize npv greenhouse gas construction project carbon emission constraint</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>matter achieve infrastructure sustainability project management practice preliminary study critical factor</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>measure sustainability construction project lifecycle taiwan lesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>method choice industrial hall wall variant optimization</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>modeling sustainable earn value management evm grey uncertain condition</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>moderate role sustainable leadership relationship sustainable project management success empirical test public sector development program</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>modify ground theory conduct systematic research study sustainable project management field</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>morphology traditional landscape inland spain potential rural build environment sustainable future</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>multicriteria decisionmaking model choose good option sustainable construction management</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>multimode resourceconstraine project scheduling problem material order timeofuse electricity tariff carbon taxis</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>municipal community center healthy setting evaluation realworld health promotion intervention jerusalem</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>navigate future megaproject sustainability comprehensive framework research agenda</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>navigate sustainable project management construction explore differential impact coercive pressure ethical responsibility importanceperformance matrix analysis ipma</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>new multiobjective optimization approach sustainable project portfolio selection real world application intervalvalue fuzzy environment</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>new multiperiod optimization model resilientsustainable project portfolio evaluation intervalvalue pythagorean fuzzy set case study</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>new sustainability framework urban underground space</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>nexus project management approach sustainable development innovative behavior mechanism polish financial industry</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>novel qualityembedde earn value performance analysis tool sustainable project portfolio production</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>opensource collaborative projectbase learn engineering education situation resource challenge</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>optimize application sustainable development strategy international engineering project management</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>organization stakeholder role influence implement sustainability requirement construction project</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>paradigm shift sustainability waterbased power sector application hydropower sustainability assessment protocol</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>paradoxical profession project management contradictory nature sustainable project objective</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>passive lowenergy design green star strategy green starrate building south africa</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>perceive environmental leadership influence employee green behavior construction industry mediate role environmental awareness moderate role perceive proenvironmental climate</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>perceive regulation influence environmentally sustainable project management mediate role commitment moderate role triple constraint</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>performance evaluation sustainable project possibilistic integrate novel analytic hierarchy processdata envelopment analysis approach znumber information</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>phase interdependent methodology sustainable project portfolio planning pharmaceutical industry</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>pillar sustainability agile project management influence</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>plan investment fail consequence traffic forecast effect ppp contract portuguese brazilian case</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>plssem model optimize delhi metro blue line performance integration sustainability infrastructure project management</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>postproject sustainability evaluation complex system approach framework application revolve loan fund microfinance project indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>prediction risk delay construction project hybrid artificial intelligence model</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>preemptive nonpreemptive multiskill multimode resourceconstraine project scheduling problem consider sustainability energy consumption comprehensive mathematical model</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>prioritize stakeholder collaborative research innovation project sustainability</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>profiling employability skill life cycle professional amid circular digital economy</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>project control practice enable sustainable project management</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>project implementation scenario selection sustainable project product lifecycle management application network data envelopment analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>project lifecycle readiness approach manage construction waste jordan</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>project management biotech context explore interrelation maturity sustainable project management</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>project management practice lead infrastructure sustainable success empirical study base goalsetting theory</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>project management sustainability playing trick treat planet</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>project management sustainable building comprehensive insight relationship project success</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>project workplace observation project manager rd projectintensive company</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>promote career counselor sustainable career development groupbase life construction dialogue intervention construct future purposeful life</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>promote owner bim adoption behavior achieve sustainable project management</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>proposal multicriteria decisionmaking model biogas production</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>qualitative stakeholder analysis swedish regional biogas development thematic network approach</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>recycle waste crystallinesilicon solar cell application high performance sibase anode material lithiumion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>relevant criterion select project delivery method sustainable construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>rethink project life cycle circularity challenge process role governance</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>revisit relationship sustainable project management project success moderate role stakeholder engagement team build</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>riskbase metanetwork modeling sustainable project performance international construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>role bim sustainable construction project delivery method focus circular economy</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>role competencybase certification ensure sustainable project delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>role energyscape element create sustainable economic project egyptian park</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>role paradigm shift project management investigate project manager competency require sustainable project management</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>runoff infiltration response revegetate slope clip management northern loess plateau</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>russian arctic mineral resource sustainable development context energy transition esg agenda geopolitical tension</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>schedule optimization use value engineering npv maximization</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>search crowd sustainable tourism leisure project</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>secondary datum research social sustainability construction project management transition interview society projectaspractice</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>set standard infrastructure sustainability</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>simulation project management education impact awareness ability navigate project sustainable way</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>snapshot geriatric rehabilitation year experience</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>social conflict management framework project viability case study korean megaproject</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>spherical sustainability construction demolition align policy goal regulation market stakeholder mindset</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>stakeholder managementone clue sustainable project managementa underestimate factor project success small construction company</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>structural equation model assess effect strategic project relate potential risk project delivery qatar</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>structural equation model assess impact sustainability management success construction project</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>structural model antecedent sustainable project management pakistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>study majoraccident risk assessment technique environmental impact assessment process</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>success factor management development project</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>success renewable energy project financial nonfinancial performance measure</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>support early career project manager construction multivocal study</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>survey valorization wood agribusiness waste application fossil carbon substitute metallurgical process</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>sustain consistent condom use female sex worker address vulnerability strengthen communityled organization india</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>sustainability assessment construction project costsustainability tradeoff approach</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>sustainability high education institution case study project fucape sustainable</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>sustainability infrastructure project managementanalysis european megaproject</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>sustainability international research evidence h european project</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>sustainability intervention construction project managersestablishe minimum baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>sustainability new school think project management</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>sustainability project management pm versus prism</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>sustainability project management practice</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>sustainability project management project success virtual team quantitative analysis consider stakeholder engagement knowledge management</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>sustainability software development project leadership core selfevaluation empowerment critical success factor</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>sustainability success variable project management context expert panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>sustainabilityoriente project scheduling base zfuzzy number public institution</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>sustainable building project management algeria challenge strategy future direction environmentally friendly construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>sustainable development digital cultural heritage hybrid analysis crowdsourcing project fsqca system dynamic</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>sustainable infrastructure design framework integration rating system build information modeling</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>sustainable infrastructure project selection new group decisionmaking framework introduce mora method interval type fuzzy environment</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>sustainable innovation project partnership high education institution challenge implication stakeholder engagement</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>sustainable metric project financial risk management</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>sustainable multiobjective multimode resourceconstraine project scheduling problem solve new reduce bucket search matheuristic algorithm</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>sustainable operation selection oil gas project</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>sustainable project management evaluation relationshipspecific risk risk determinant threaten achieve intend benefit interorganizational cooperation engineering project</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>sustainable project management practice lesson covid pandemic significant change method</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>sustainable project management project control infrastructure project</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>sustainable project management reduce risk cost inaccuracy plssem approach</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>sustainable project management strategy multitaske situation viewpoint cognitive mechanism motivational belief</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>sustainable project performance remote work setting learning covid pandemica case study malaysia</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>sustainable project portfolio selection optimization consideration outsource decision financing option staff assignment interval type fuzzy uncertainty</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>sustainable project scheduling reduce environmental pollution project fuzzy multiobjective programming approach case study eastern iran</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>sustainable project selection optimal project selection consider sustainability reinvestment strategy</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>sustainable project selection scheduling scenariobase stochastic programming case study industrial project</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>sustainable project success entrepreneurial leadership insight big datum analytic ipma nca integration</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>sustainable projectbased learn methodology adaptable technological advance web programming</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>sustainable risk management enterprise</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>sustainable swedish school intervention extra aerobic exerciseit organization effect physical fitness academic achievement</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>sustainable urban development role megaproject expert view madrid nuevo norte project</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>synergy share leadership unveil role innovative work behavior knowledge management project success</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>systematic literature review concern different interpretation role sustainability project management</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>systemic insight value creation solar pv energy market project management system impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>take stock communitybase flood risk management malawi different stakeholder different perspective</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>technical economic aspect environmentally sustainable investment term eu taxonomy</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>think twice achieve sustainable project management ecological sustainability sustainable project management cube model</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>understand responsible compute project management sustainability</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>understand risk culture context sustainable project preliminary study</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>understand role build environment resilience natural disaster lesson learn wenchuan earthquake</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>unlock source individual readiness change explore role nationality</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>unlock sustainable project management role project manager competency resource bricolage stakeholder engagement perspective</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>unveil antecedent career sustainability project management</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>value creation sustainable project management case study leading soe china</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>webbased decision support system project evaluation sustainable development consideration base develop pythagorean fuzzy decision method</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>work readinesscareer resilience linkage implication project talent management</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>year sustainable project know literature say</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>yes construction cost time scope important new action plan infrastructure success</t>
         </is>
       </c>
     </row>
